--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00126_19130805.6" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00126_19130805.6" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -991,7 +991,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00126_19130805.6" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00126_19130805.6" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y93"/>
+  <dimension ref="A1:Y76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: ä¸“</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+4E13 CJK UNIFIED IDEOGRAPH-4E13 | isolated marker/symbol line :: 专</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 152â€¢TE</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L52: isolated marker/symbol line :: j +</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -646,7 +650,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L189: line starts with digit/letter garbage token | suspicious token(s): 1The (letter/digit mix) :: 1The free-for-all pace, which rumor</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •RIGHT•</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -673,7 +677,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -700,19 +704,19 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: ä¸“</t>
+          <t>L68: stray/suspicious non-ASCII glyph(s): U+4E13 CJK UNIFIED IDEOGRAPH-4E13 | isolated marker/symbol line :: 专</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Buyin â‚¬</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 152•TE</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: ä¸“</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+4E13 CJK UNIFIED IDEOGRAPH-4E13 | isolated marker/symbol line :: 专</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -733,7 +737,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L471: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: ******* â€¢â€¢â€¢â€¢</t>
+          <t>L189: line starts with digit/letter garbage token | suspicious token(s): 1The (letter/digit mix) :: 1The free-for-all pace, which rumor</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -772,7 +776,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>L808: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 02000030x (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Jersey 00001000000001 213" vs "02000030x 7 11" :: . .02000030xâ€”7 11 1</t>
+          <t>L808: suspicious token(s): 02000030x (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Jersey 00001000000001 213" vs "02000030x 7 11" :: . .02000030x—7 11 1</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
@@ -787,19 +791,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Kalamazoo, Mich., Aug.â€” Feature-</t>
+          <t>L189: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢RIGHTâ€¢</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Buyin €</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: ä¸“</t>
+          <t>L68: stray/suspicious non-ASCII glyph(s): U+4E13 CJK UNIFIED IDEOGRAPH-4E13 | isolated marker/symbol line :: 专</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -814,13 +818,13 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John. ... 32</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John. ... 32</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L478: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----------0 F -</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -838,24 +842,24 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "Baltimore 000111000 3 At Buffalo 6 1" vs "" :: Baltimore. ... 000111000 â€” 3</t>
+          <t>L602: punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "Baltimore 000111000 3 At Buffalo 6 1" vs "" :: Baltimore. ... 000111000 — 3</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "102000310712 low McGraynor Mattern Smith and" vs "102000310 7 12" :: Brooklyn .........102000310â€”7 12</t>
+          <t>L853: punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "102000310712 low McGraynor Mattern Smith and" vs "102000310 7 12" :: Brooklyn .........102000310—7 12</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
@@ -870,12 +874,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Philadelphia, Aug. 4 â€” Accused of</t>
+          <t>L287: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Time-2.06 ½， 2.05 ½， 2.07%.</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Chicago, Aug. 4â€”The pace set By</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •RIGHT•</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -897,13 +901,13 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L439: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John ...618</t>
+          <t>L439: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John ...618</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L916: line starts with punctuation glued to text :: **THE HOUSE. OF GOOD CLOTHES"</t>
+          <t>L366: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton 27</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -949,12 +953,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L389: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Me for Hankâ€™s Pne Tree Circuit</t>
+          <t>L220: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -976,11 +980,15 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. Croix .. .586</t>
+          <t>L441: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. Croix .. .586</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L440: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton . .586</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1010,7 +1018,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York... . 00000150x â€” 614</t>
+          <t>L569: punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York... . 00000150x — 614</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
@@ -1020,12 +1028,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L481: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At St. Louis â€”</t>
+          <t>L595: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON :: Chicago:：. 001000000-14</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: -last week. Stafford, Fred Jamiesonâ€™s</t>
+          <t>L308: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ League Standing</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1047,11 +1055,15 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 â€”</t>
+          <t>L446: punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 —</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L478: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----------0 F -</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1091,12 +1103,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L487: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Washington â€”</t>
+          <t>L654: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L334: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1122,7 +1134,11 @@
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L916: line starts with punctuation glued to text :: **THE HOUSE. OF GOOD CLOTHES"</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
@@ -1160,14 +1176,10 @@
           <t>L227: suspicious token(s): 17c (letter/digit mix) :: LISLE SOX, only 17c. a pair. Younever</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L488: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis. ... 021000000 â€” 3</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L269: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Kalamazoo, Mich., -Aug.â€” Feature-</t>
+          <t>L335: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Pct. •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1209,12 +1221,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1231,21 +1243,17 @@
           <t>L228: suspicious token(s): 25c (letter/digit mix) :: buy these less than 25c.</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Washington. ... 020010000 â€” 310</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L308: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ League Standing</t>
+          <t>L336: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .604•</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L189: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1285,7 +1293,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1299,17 +1307,13 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L808: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 02000030x (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Jersey 00001000000001 213" vs "02000030x 7 11" :: . .02000030xâ€”7 11 1</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L504: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Russell, Cicotte and</t>
-        </is>
-      </c>
+          <t>L808: suspicious token(s): 02000030x (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Jersey 00001000000001 213" vs "02000030x 7 11" :: . .02000030x—7 11 1</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Philadelphia, Aug. 4â€”Accused of</t>
+          <t>L337: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1351,12 +1355,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1366,17 +1370,13 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L520: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Philadelphia â€”</t>
-        </is>
-      </c>
+          <t>L820: punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150x—6 14 1</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L338: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>L488: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis. ... 021000000 â€” 3</t>
+          <t>L488: punctuation artifact: repeated periods :: St. Louis. ... 021000000 — 3</t>
         </is>
       </c>
       <c r="Q12" s="1" t="inlineStr">
@@ -1433,17 +1433,13 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L539: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Falkenberg,</t>
-        </is>
-      </c>
+          <t>L872: punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223x—13 19 1</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L335: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Pct. â€¢</t>
+          <t>L339: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .265 •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1490,7 +1486,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1499,14 +1495,10 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L558: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At New York â€”</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L336: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .604â€¢</t>
+          <t>L341: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
@@ -1523,12 +1515,12 @@
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Washington. ... 020010000 â€” 310</t>
+          <t>L500: punctuation artifact: repeated periods :: Washington. ... 020010000 — 310</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Philadelphia. .. .000000402â€”6 10 3</t>
+          <t>L732: punctuation artifact: repeated periods :: Philadelphia. .. .000000402—6 10 3</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1562,14 +1554,10 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L567: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Toronto. 020000000 â€” 28</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .563â€¢</t>
+          <t>L343: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
@@ -1581,7 +1569,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L220: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -1591,7 +1579,7 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis.........021000000â€”3 7 0</t>
+          <t>L734: punctuation artifact: repeated periods :: St. Louis.........021000000—3 7 0</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1625,14 +1613,10 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York... . 00000150x â€” 614</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L338: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .563â€¢</t>
+          <t>L344: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
@@ -1654,7 +1638,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Chicago .........300200000â€”5 4</t>
+          <t>L744: punctuation artifact: repeated periods :: Chicago .........300200000—5 4</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1688,14 +1672,10 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L571: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Coakley an</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .265 â€¢</t>
+          <t>L345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Lose •</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
@@ -1739,14 +1719,10 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Montreal â€”</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L346: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Two. •</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
@@ -1758,7 +1734,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L334: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -1790,14 +1766,10 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L590: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Chicago â€”</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L347: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .582•</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr"/>
@@ -1809,12 +1781,12 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L336: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .604•</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York... . 00000150x â€” 614</t>
+          <t>L569: punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York... . 00000150x — 614</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
@@ -1841,14 +1813,10 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "Baltimore 000111000 3 At Buffalo 6 1" vs "" :: Baltimore. ... 000111000 â€” 3</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L348: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr"/>
@@ -1860,7 +1828,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L337: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1870,7 +1838,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L790: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Montreal ..........30300100201â€”7 10 3</t>
+          <t>L790: punctuation artifact: repeated periods :: Montreal ..........30300100201—7 10 3</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -1892,14 +1860,10 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L603: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Buffalo â€”</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>L345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Lose â€¢</t>
+          <t>L349: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr"/>
@@ -1911,7 +1875,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L338: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -1921,7 +1885,7 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L799: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Baltimore...........000111000â€”3 6 1</t>
+          <t>L799: punctuation artifact: repeated periods :: Baltimore...........000111000—3 6 1</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -1943,14 +1907,10 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Pittsburg â€”</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>L346: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Two. â€¢</t>
+          <t>L350: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | symbol-only separator/garbage line :: .255 ♦</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr"/>
@@ -1962,7 +1922,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L339: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .265 •</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -1972,7 +1932,7 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L801: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Buffalo ............000000010â€”1 6 0</t>
+          <t>L801: punctuation artifact: repeated periods :: Buffalo ............000000010—1 6 0</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1994,14 +1954,10 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L633: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Cincinnati â€”</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>L347: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .582â€¢</t>
+          <t>L352: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr"/>
@@ -2013,17 +1969,17 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L356: isolated marker/symbol line :: 21</t>
+          <t>L341: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "Baltimore 000111000 3 At Buffalo 6 1" vs "" :: Baltimore. ... 000111000 â€” 3</t>
+          <t>L602: punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "Baltimore 000111000 3 At Buffalo 6 1" vs "" :: Baltimore. ... 000111000 — 3</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Detroit..........002000002â€”4 15 3</t>
+          <t>L818: punctuation artifact: repeated periods :: Detroit..........002000002—4 15 3</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2045,14 +2001,10 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Boston. ... 120000001 â€” 4</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .540â€¢</t>
+          <t>L353: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • • • •</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr"/>
@@ -2064,7 +2016,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L357: isolated marker/symbol line :: 21</t>
+          <t>L343: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -2074,7 +2026,7 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
+          <t>L820: punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150x—6 14 1</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
@@ -2096,14 +2048,10 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .540â€¢</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr"/>
@@ -2115,7 +2063,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L358: symbol-only separator/garbage line :: 27 21</t>
+          <t>L344: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -2150,7 +2098,7 @@
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>L350: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: .255 â™¦</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John. ... 32</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr"/>
@@ -2162,7 +2110,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L360: isolated marker/symbol line :: 36</t>
+          <t>L347: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .582•</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -2172,7 +2120,7 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "102000310712 low McGraynor Mattern Smith and" vs "102000310 7 12" :: Brooklyn .........102000310â€”7 12</t>
+          <t>L853: punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "102000310712 low McGraynor Mattern Smith and" vs "102000310 7 12" :: Brooklyn .........102000310—7 12</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -2197,7 +2145,7 @@
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L366: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton 27</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr"/>
@@ -2209,7 +2157,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L410: isolated marker/symbol line :: Â°</t>
+          <t>L348: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -2219,7 +2167,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L862: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: New York.........000001100â€”2 7 0</t>
+          <t>L862: punctuation artifact: repeated periods :: New York.........000001100—2 7 0</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2244,7 +2192,7 @@
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢ â€¢ â€¢</t>
+          <t>L406: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ St. Croix.</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr"/>
@@ -2256,17 +2204,17 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L349: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Boston. ... 120000001 â€” 4</t>
+          <t>L639: punctuation artifact: repeated periods :: Boston. ... 120000001 — 4</t>
         </is>
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Pittsburg .......000000010â€”1 3 1</t>
+          <t>L864: punctuation artifact: repeated periods :: Pittsburg .......000000010—1 3 1</t>
         </is>
       </c>
       <c r="R28" s="1" t="inlineStr"/>
@@ -2291,7 +2239,7 @@
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>L362: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢1</t>
+          <t>L408: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ Bangor.........13</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr"/>
@@ -2303,13 +2251,13 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L350: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | symbol-only separator/garbage line :: .255 ♦</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
+          <t>L872: punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223x—13 19 1</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2334,7 +2282,7 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John. ... 32</t>
+          <t>L411: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr"/>
@@ -2346,13 +2294,13 @@
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L413: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L352: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Boston..........120000001â€” 4 7 1</t>
+          <t>L874: punctuation artifact: repeated periods :: Boston..........120000001— 4 7 1</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2377,7 +2325,7 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Fredericton 27</t>
+          <t>L412: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr"/>
@@ -2389,7 +2337,7 @@
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L353: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • • • •</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2416,7 +2364,7 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>L384: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Charlie Oâ€™Brien, the St. John club's</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr"/>
@@ -2428,7 +2376,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L426: isolated marker/symbol line :: p</t>
+          <t>L356: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2455,7 +2403,7 @@
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ St. Croix.</t>
+          <t>L414: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr"/>
@@ -2467,7 +2415,7 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L427: isolated marker/symbol line :: I.</t>
+          <t>L357: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2494,7 +2442,7 @@
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>L408: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ Bangor.........13</t>
+          <t>L439: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John ...618</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr"/>
@@ -2506,7 +2454,7 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L431: symbol-only separator/garbage line :: .600</t>
+          <t>L358: symbol-only separator/garbage line :: 27 21</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2533,7 +2481,7 @@
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L440: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton . .586</t>
         </is>
       </c>
       <c r="L35" s="1" t="inlineStr"/>
@@ -2545,7 +2493,7 @@
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L432: symbol-only separator/garbage line :: .560</t>
+          <t>L360: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2572,7 +2520,7 @@
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L441: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. Croix .. .586</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr"/>
@@ -2584,7 +2532,7 @@
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L433: symbol-only separator/garbage line :: .560</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2611,7 +2559,7 @@
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>L413: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L442: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ Bangor . . . .294</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr"/>
@@ -2623,7 +2571,7 @@
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L434: symbol-only separator/garbage line :: .275</t>
+          <t>L410: isolated marker/symbol line :: °</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2650,7 +2598,7 @@
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L471: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: ******* ••••</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr"/>
@@ -2662,7 +2610,7 @@
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L758: isolated marker/symbol line :: 1</t>
+          <t>L411: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2689,7 +2637,7 @@
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>L439: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John ...618</t>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L39" s="1" t="inlineStr"/>
@@ -2701,7 +2649,7 @@
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L759: isolated marker/symbol line :: 4</t>
+          <t>L412: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2726,11 +2674,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L440: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Fredericton . .586</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
@@ -2740,7 +2684,7 @@
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L840: isolated marker/symbol line :: %</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2765,11 +2709,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. Croix .. .586</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
@@ -2779,7 +2719,7 @@
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L414: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2804,11 +2744,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ Bangor . . . .294</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
@@ -2818,7 +2754,7 @@
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L844: symbol-only separator/garbage line | punctuation artifact: repeated exclamation marks :: 2/1/07!!!!!!!!!!!!!!</t>
+          <t>L426: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2843,11 +2779,7 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 â€”</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
@@ -2857,7 +2789,7 @@
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L846: symbol-only separator/garbage line :: 20 22</t>
+          <t>L427: isolated marker/symbol line :: I.</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2882,21 +2814,17 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L456: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Timeâ€”2.06%2, 2.05%, 2.07%.</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L486: isolated marker/symbol line :: 3</t>
+          <t>L389: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L881: isolated marker/symbol line :: a</t>
+          <t>L431: symbol-only separator/garbage line :: .600</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2921,21 +2849,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L471: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: ******* â€¢â€¢â€¢â€¢</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L489: isolated marker/symbol line :: 7</t>
+          <t>L486: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L886: isolated marker/symbol line :: :</t>
+          <t>L432: symbol-only separator/garbage line :: .560</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2960,19 +2884,19 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”JUST A FEWâ€”</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L490: isolated marker/symbol line :: 0</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L489: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L433: symbol-only separator/garbage line :: .560</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2995,19 +2919,19 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Timeâ€”2.12, 2.08%, 1.07.</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L495: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L490: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L434: symbol-only separator/garbage line :: .275</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3030,19 +2954,19 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Wilmington, Del., Aug. 4â€”"Buck"</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L501: isolated marker/symbol line :: 4</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr"/>
+          <t>L495: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>L471: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: ******* ••••</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr"/>
       <c r="R48" s="1" t="inlineStr"/>
@@ -3065,19 +2989,19 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Next Game at Scullyâ€™s</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L526: isolated marker/symbol line :: 2</t>
-        </is>
-      </c>
-      <c r="O49" s="1" t="inlineStr"/>
+          <t>L501: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>L758: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P49" s="1" t="inlineStr"/>
       <c r="Q49" s="1" t="inlineStr"/>
       <c r="R49" s="1" t="inlineStr"/>
@@ -3100,19 +3024,19 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L577: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: oneâ€� yesterday. Lajoie, while at bat,</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L528: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O50" s="1" t="inlineStr"/>
+          <t>L526: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>L759: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr"/>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3135,19 +3059,19 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L599: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Oâ€™Loughlin, and Sheridan was appeal-</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L533: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O51" s="1" t="inlineStr"/>
+          <t>L528: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>L806: symbol-only separator/garbage line :: .010000000—1 2 2</t>
+        </is>
+      </c>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr"/>
       <c r="R51" s="1" t="inlineStr"/>
@@ -3170,19 +3094,19 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L710: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Morey or PetÃ¨ Condon the other,</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L535: isolated marker/symbol line :: 4</t>
-        </is>
-      </c>
-      <c r="O52" s="1" t="inlineStr"/>
+          <t>L533: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>L840: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr"/>
       <c r="R52" s="1" t="inlineStr"/>
@@ -3205,19 +3129,19 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: at St. John to-morrow.â€”J. D. B.</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L542: isolated marker/symbol line :: V</t>
-        </is>
-      </c>
-      <c r="O53" s="1" t="inlineStr"/>
+          <t>L535: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr"/>
       <c r="R53" s="1" t="inlineStr"/>
@@ -3240,19 +3164,19 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L730: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At St Louisâ€”</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: 4</t>
-        </is>
-      </c>
-      <c r="O54" s="1" t="inlineStr"/>
+          <t>L542: isolated marker/symbol line :: V</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>L844: symbol-only separator/garbage line | punctuation artifact: repeated exclamation marks :: 2/1/07!!!!!!!!!!!!!!</t>
+        </is>
+      </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr"/>
       <c r="R54" s="1" t="inlineStr"/>
@@ -3275,19 +3199,19 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Philadelphia. .. .000000402â€”6 10 3</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L566: isolated marker/symbol line :: 3</t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="inlineStr"/>
+          <t>L560: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>L846: symbol-only separator/garbage line :: 20 22</t>
+        </is>
+      </c>
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr"/>
       <c r="R55" s="1" t="inlineStr"/>
@@ -3310,19 +3234,19 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis.........021000000â€”3 7 0</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L568: isolated marker/symbol line :: 0</t>
-        </is>
-      </c>
-      <c r="O56" s="1" t="inlineStr"/>
+          <t>L566: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>L881: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr"/>
       <c r="R56" s="1" t="inlineStr"/>
@@ -3345,19 +3269,19 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L742: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Washingtonâ€”</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L570: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O57" s="1" t="inlineStr"/>
+          <t>L568: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>L886: isolated marker/symbol line :: :</t>
+        </is>
+      </c>
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
       <c r="R57" s="1" t="inlineStr"/>
@@ -3380,16 +3304,12 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Chicago .........300200000â€”5 4</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L574: isolated marker/symbol line :: A</t>
+          <t>L570: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3415,16 +3335,12 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Washington. . . .020010000â€”3 10</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L577: isolated marker/symbol line :: 9</t>
+          <t>L574: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3450,16 +3366,12 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L748: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Russell. Cicotte and</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L583: isolated marker/symbol line :: 3</t>
+          <t>L577: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3485,16 +3397,12 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L768: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Torontoâ€”First game:</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L587: isolated marker/symbol line :: 3</t>
+          <t>L583: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3520,16 +3428,12 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Jersey. . . .00001000000001â€”2 13 1</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L589: isolated marker/symbol line :: 2</t>
+          <t>L587: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3555,16 +3459,12 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Toronto. . . .00000001000000â€”1 12 4</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L591: isolated marker/symbol line :: 2</t>
+          <t>L589: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3590,16 +3490,12 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Montrealâ€”</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L596: isolated marker/symbol line :: 1</t>
+          <t>L591: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3625,16 +3521,12 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L788: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Providence. . . .10200120000â€”6 13 3</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L604: isolated marker/symbol line :: 6</t>
+          <t>L596: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3660,16 +3552,12 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L790: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Montreal ..........30300100201â€”7 10 3</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L605: isolated marker/symbol line :: 1</t>
+          <t>L604: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3695,16 +3583,12 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L792: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 2 Batteriesâ€”Sline, Reisigi and Ons-</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L608: isolated marker/symbol line :: 6</t>
+          <t>L605: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3730,16 +3614,12 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L797: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Buffaloâ€”</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L609: isolated marker/symbol line :: 0</t>
+          <t>L608: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3765,16 +3645,12 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L799: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Baltimore...........000111000â€”3 6 1</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L614: isolated marker/symbol line :: 3</t>
+          <t>L609: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3800,16 +3676,12 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L801: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Buffalo ............000000010â€”1 6 0</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L615: isolated marker/symbol line :: 1</t>
+          <t>L614: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3835,16 +3707,12 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Roth and Egan; Bebe,</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L634: isolated marker/symbol line :: 1</t>
+          <t>L615: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3870,16 +3738,12 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L806: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: .010000000â€”1 2 2</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L640: isolated marker/symbol line :: 7</t>
+          <t>L634: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -3905,16 +3769,12 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L808: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 02000030x (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Jersey 00001000000001 213" vs "02000030x 7 11" :: . .02000030xâ€”7 11 1</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L641: isolated marker/symbol line :: 1</t>
+          <t>L640: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -3940,16 +3800,12 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L810: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Falkenberk, Kahler,</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L653: isolated marker/symbol line :: 6</t>
+          <t>L641: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -3975,16 +3831,12 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L816: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At New Yorkâ€”</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L653: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -4010,14 +3862,14 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Detroit..........002000002â€”4 15 3</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
-      <c r="N76" s="1" t="inlineStr"/>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t>L654: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
       <c r="O76" s="1" t="inlineStr"/>
       <c r="P76" s="1" t="inlineStr"/>
       <c r="Q76" s="1" t="inlineStr"/>
@@ -4030,533 +3882,6 @@
       <c r="X76" s="1" t="inlineStr"/>
       <c r="Y76" s="1" t="inlineStr"/>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr"/>
-      <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" s="1" t="inlineStr"/>
-      <c r="D77" s="1" t="inlineStr"/>
-      <c r="E77" s="1" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr"/>
-      <c r="M77" s="1" t="inlineStr"/>
-      <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr"/>
-      <c r="P77" s="1" t="inlineStr"/>
-      <c r="Q77" s="1" t="inlineStr"/>
-      <c r="R77" s="1" t="inlineStr"/>
-      <c r="S77" s="1" t="inlineStr"/>
-      <c r="T77" s="1" t="inlineStr"/>
-      <c r="U77" s="1" t="inlineStr"/>
-      <c r="V77" s="1" t="inlineStr"/>
-      <c r="W77" s="1" t="inlineStr"/>
-      <c r="X77" s="1" t="inlineStr"/>
-      <c r="Y77" s="1" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr"/>
-      <c r="B78" s="1" t="inlineStr"/>
-      <c r="C78" s="1" t="inlineStr"/>
-      <c r="D78" s="1" t="inlineStr"/>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L822: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Willett, Dubue and Mc-</t>
-        </is>
-      </c>
-      <c r="L78" s="1" t="inlineStr"/>
-      <c r="M78" s="1" t="inlineStr"/>
-      <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr"/>
-      <c r="P78" s="1" t="inlineStr"/>
-      <c r="Q78" s="1" t="inlineStr"/>
-      <c r="R78" s="1" t="inlineStr"/>
-      <c r="S78" s="1" t="inlineStr"/>
-      <c r="T78" s="1" t="inlineStr"/>
-      <c r="U78" s="1" t="inlineStr"/>
-      <c r="V78" s="1" t="inlineStr"/>
-      <c r="W78" s="1" t="inlineStr"/>
-      <c r="X78" s="1" t="inlineStr"/>
-      <c r="Y78" s="1" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr"/>
-      <c r="B79" s="1" t="inlineStr"/>
-      <c r="C79" s="1" t="inlineStr"/>
-      <c r="D79" s="1" t="inlineStr"/>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr"/>
-      <c r="R79" s="1" t="inlineStr"/>
-      <c r="S79" s="1" t="inlineStr"/>
-      <c r="T79" s="1" t="inlineStr"/>
-      <c r="U79" s="1" t="inlineStr"/>
-      <c r="V79" s="1" t="inlineStr"/>
-      <c r="W79" s="1" t="inlineStr"/>
-      <c r="X79" s="1" t="inlineStr"/>
-      <c r="Y79" s="1" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="1" t="inlineStr"/>
-      <c r="C80" s="1" t="inlineStr"/>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L851: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Chicagoâ€”</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" s="1" t="inlineStr"/>
-      <c r="Q80" s="1" t="inlineStr"/>
-      <c r="R80" s="1" t="inlineStr"/>
-      <c r="S80" s="1" t="inlineStr"/>
-      <c r="T80" s="1" t="inlineStr"/>
-      <c r="U80" s="1" t="inlineStr"/>
-      <c r="V80" s="1" t="inlineStr"/>
-      <c r="W80" s="1" t="inlineStr"/>
-      <c r="X80" s="1" t="inlineStr"/>
-      <c r="Y80" s="1" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr"/>
-      <c r="B81" s="1" t="inlineStr"/>
-      <c r="C81" s="1" t="inlineStr"/>
-      <c r="D81" s="1" t="inlineStr"/>
-      <c r="E81" s="1" t="inlineStr"/>
-      <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "102000310712 low McGraynor Mattern Smith and" vs "102000310 7 12" :: Brooklyn .........102000310â€”7 12</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr"/>
-      <c r="R81" s="1" t="inlineStr"/>
-      <c r="S81" s="1" t="inlineStr"/>
-      <c r="T81" s="1" t="inlineStr"/>
-      <c r="U81" s="1" t="inlineStr"/>
-      <c r="V81" s="1" t="inlineStr"/>
-      <c r="W81" s="1" t="inlineStr"/>
-      <c r="X81" s="1" t="inlineStr"/>
-      <c r="Y81" s="1" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr"/>
-      <c r="E82" s="1" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L855: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Chicago. . . . . .001000000â€”1 4</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
-      <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr"/>
-      <c r="R82" s="1" t="inlineStr"/>
-      <c r="S82" s="1" t="inlineStr"/>
-      <c r="T82" s="1" t="inlineStr"/>
-      <c r="U82" s="1" t="inlineStr"/>
-      <c r="V82" s="1" t="inlineStr"/>
-      <c r="W82" s="1" t="inlineStr"/>
-      <c r="X82" s="1" t="inlineStr"/>
-      <c r="Y82" s="1" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="1" t="inlineStr"/>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L857: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Allen and Miller; Moore,</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr"/>
-      <c r="R83" s="1" t="inlineStr"/>
-      <c r="S83" s="1" t="inlineStr"/>
-      <c r="T83" s="1" t="inlineStr"/>
-      <c r="U83" s="1" t="inlineStr"/>
-      <c r="V83" s="1" t="inlineStr"/>
-      <c r="W83" s="1" t="inlineStr"/>
-      <c r="X83" s="1" t="inlineStr"/>
-      <c r="Y83" s="1" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr"/>
-      <c r="B84" s="1" t="inlineStr"/>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr"/>
-      <c r="E84" s="1" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L860: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Pittsburgâ€”</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
-      <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr"/>
-      <c r="R84" s="1" t="inlineStr"/>
-      <c r="S84" s="1" t="inlineStr"/>
-      <c r="T84" s="1" t="inlineStr"/>
-      <c r="U84" s="1" t="inlineStr"/>
-      <c r="V84" s="1" t="inlineStr"/>
-      <c r="W84" s="1" t="inlineStr"/>
-      <c r="X84" s="1" t="inlineStr"/>
-      <c r="Y84" s="1" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="1" t="inlineStr"/>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L862: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: New York.........000001100â€”2 7 0</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr"/>
-      <c r="R85" s="1" t="inlineStr"/>
-      <c r="S85" s="1" t="inlineStr"/>
-      <c r="T85" s="1" t="inlineStr"/>
-      <c r="U85" s="1" t="inlineStr"/>
-      <c r="V85" s="1" t="inlineStr"/>
-      <c r="W85" s="1" t="inlineStr"/>
-      <c r="X85" s="1" t="inlineStr"/>
-      <c r="Y85" s="1" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="1" t="inlineStr"/>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Pittsburg .......000000010â€”1 3 1</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr"/>
-      <c r="R86" s="1" t="inlineStr"/>
-      <c r="S86" s="1" t="inlineStr"/>
-      <c r="T86" s="1" t="inlineStr"/>
-      <c r="U86" s="1" t="inlineStr"/>
-      <c r="V86" s="1" t="inlineStr"/>
-      <c r="W86" s="1" t="inlineStr"/>
-      <c r="X86" s="1" t="inlineStr"/>
-      <c r="Y86" s="1" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr"/>
-      <c r="B87" s="1" t="inlineStr"/>
-      <c r="C87" s="1" t="inlineStr"/>
-      <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L866: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Demaree, Marquard and</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr"/>
-      <c r="R87" s="1" t="inlineStr"/>
-      <c r="S87" s="1" t="inlineStr"/>
-      <c r="T87" s="1" t="inlineStr"/>
-      <c r="U87" s="1" t="inlineStr"/>
-      <c r="V87" s="1" t="inlineStr"/>
-      <c r="W87" s="1" t="inlineStr"/>
-      <c r="X87" s="1" t="inlineStr"/>
-      <c r="Y87" s="1" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr"/>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L870: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Cincinnatiâ€”</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
-      <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr"/>
-      <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr"/>
-      <c r="R88" s="1" t="inlineStr"/>
-      <c r="S88" s="1" t="inlineStr"/>
-      <c r="T88" s="1" t="inlineStr"/>
-      <c r="U88" s="1" t="inlineStr"/>
-      <c r="V88" s="1" t="inlineStr"/>
-      <c r="W88" s="1" t="inlineStr"/>
-      <c r="X88" s="1" t="inlineStr"/>
-      <c r="Y88" s="1" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr"/>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
-      <c r="F89" s="1" t="inlineStr"/>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr"/>
-      <c r="R89" s="1" t="inlineStr"/>
-      <c r="S89" s="1" t="inlineStr"/>
-      <c r="T89" s="1" t="inlineStr"/>
-      <c r="U89" s="1" t="inlineStr"/>
-      <c r="V89" s="1" t="inlineStr"/>
-      <c r="W89" s="1" t="inlineStr"/>
-      <c r="X89" s="1" t="inlineStr"/>
-      <c r="Y89" s="1" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr"/>
-      <c r="B90" s="1" t="inlineStr"/>
-      <c r="C90" s="1" t="inlineStr"/>
-      <c r="D90" s="1" t="inlineStr"/>
-      <c r="E90" s="1" t="inlineStr"/>
-      <c r="F90" s="1" t="inlineStr"/>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Boston..........120000001â€” 4 7 1</t>
-        </is>
-      </c>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
-      <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr"/>
-      <c r="P90" s="1" t="inlineStr"/>
-      <c r="Q90" s="1" t="inlineStr"/>
-      <c r="R90" s="1" t="inlineStr"/>
-      <c r="S90" s="1" t="inlineStr"/>
-      <c r="T90" s="1" t="inlineStr"/>
-      <c r="U90" s="1" t="inlineStr"/>
-      <c r="V90" s="1" t="inlineStr"/>
-      <c r="W90" s="1" t="inlineStr"/>
-      <c r="X90" s="1" t="inlineStr"/>
-      <c r="Y90" s="1" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr"/>
-      <c r="B91" s="1" t="inlineStr"/>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr"/>
-      <c r="E91" s="1" t="inlineStr"/>
-      <c r="F91" s="1" t="inlineStr"/>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Rudolph, Noyes</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr"/>
-      <c r="M91" s="1" t="inlineStr"/>
-      <c r="N91" s="1" t="inlineStr"/>
-      <c r="O91" s="1" t="inlineStr"/>
-      <c r="P91" s="1" t="inlineStr"/>
-      <c r="Q91" s="1" t="inlineStr"/>
-      <c r="R91" s="1" t="inlineStr"/>
-      <c r="S91" s="1" t="inlineStr"/>
-      <c r="T91" s="1" t="inlineStr"/>
-      <c r="U91" s="1" t="inlineStr"/>
-      <c r="V91" s="1" t="inlineStr"/>
-      <c r="W91" s="1" t="inlineStr"/>
-      <c r="X91" s="1" t="inlineStr"/>
-      <c r="Y91" s="1" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr"/>
-      <c r="B92" s="1" t="inlineStr"/>
-      <c r="C92" s="1" t="inlineStr"/>
-      <c r="D92" s="1" t="inlineStr"/>
-      <c r="E92" s="1" t="inlineStr"/>
-      <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L894: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” , â€” the finest selected american leaf tobacco.</t>
-        </is>
-      </c>
-      <c r="L92" s="1" t="inlineStr"/>
-      <c r="M92" s="1" t="inlineStr"/>
-      <c r="N92" s="1" t="inlineStr"/>
-      <c r="O92" s="1" t="inlineStr"/>
-      <c r="P92" s="1" t="inlineStr"/>
-      <c r="Q92" s="1" t="inlineStr"/>
-      <c r="R92" s="1" t="inlineStr"/>
-      <c r="S92" s="1" t="inlineStr"/>
-      <c r="T92" s="1" t="inlineStr"/>
-      <c r="U92" s="1" t="inlineStr"/>
-      <c r="V92" s="1" t="inlineStr"/>
-      <c r="W92" s="1" t="inlineStr"/>
-      <c r="X92" s="1" t="inlineStr"/>
-      <c r="Y92" s="1" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr"/>
-      <c r="B93" s="1" t="inlineStr"/>
-      <c r="C93" s="1" t="inlineStr"/>
-      <c r="D93" s="1" t="inlineStr"/>
-      <c r="E93" s="1" t="inlineStr"/>
-      <c r="F93" s="1" t="inlineStr"/>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr"/>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L921: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 46.</t>
-        </is>
-      </c>
-      <c r="L93" s="1" t="inlineStr"/>
-      <c r="M93" s="1" t="inlineStr"/>
-      <c r="N93" s="1" t="inlineStr"/>
-      <c r="O93" s="1" t="inlineStr"/>
-      <c r="P93" s="1" t="inlineStr"/>
-      <c r="Q93" s="1" t="inlineStr"/>
-      <c r="R93" s="1" t="inlineStr"/>
-      <c r="S93" s="1" t="inlineStr"/>
-      <c r="T93" s="1" t="inlineStr"/>
-      <c r="U93" s="1" t="inlineStr"/>
-      <c r="V93" s="1" t="inlineStr"/>
-      <c r="W93" s="1" t="inlineStr"/>
-      <c r="X93" s="1" t="inlineStr"/>
-      <c r="Y93" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
